--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T11:11:22-05:00</t>
+    <t>2023-05-04T21:49:21-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2111,17 +2111,17 @@
   <dimension ref="A1:AP72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.60546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.8984375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2130,28 +2130,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.7109375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.0859375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.30859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.16796875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.984375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.30078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="75.84765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="242.69140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="103.8828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.7109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T21:49:21-05:00</t>
+    <t>2023-05-05T10:50:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T16:25:42-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -952,7 +952,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -979,7 +979,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU7/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU8/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
@@ -1064,7 +1064,7 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>𝗔𝗗𝗗𝗜𝗧𝗜𝗢𝗡𝗔𝗟 𝗨𝗦𝗖𝗗𝗜: The name of the test that was performed.</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1237,7 +1237,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>
@@ -2160,17 +2160,17 @@
   <dimension ref="A1:AP72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.60546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.57421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.49609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.8671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="140.1484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2179,28 +2179,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="176.73046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.16796875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="158.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="239.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="103.87890625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.7109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7286,7 +7286,7 @@
         <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.10</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-04-23T10:10:52-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1049,7 +1049,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/cibmtr-priority-variables-2022</t>
+    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.7/expansion</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -2185,7 +2185,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="158.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -2571,7 +2571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>99</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>280</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>304</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>310</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>343</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>359</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>370</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>390</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>399</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>411</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>420</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>459</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>477</v>
       </c>
@@ -10891,12 +10891,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP72">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-06-10T07:35:08-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2571,7 +2571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>99</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>280</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>304</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>310</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>343</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>359</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>370</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>390</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>399</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>411</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>420</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>459</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>477</v>
       </c>
@@ -10891,12 +10891,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP72">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-obs-priority-variables.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:49:22-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
@@ -452,7 +452,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -680,7 +680,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -719,7 +719,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -949,7 +949,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -979,7 +979,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Note that other codes are permitted, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU8/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
+    <t>Note that other codes are permitted in other slices, see [Required Bindings When Slicing by Value Sets](http://hl7.org/fhir/us/core/STU9/general-requirements.html#required-bindings-when-slicing-by-valuesets)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-clinical-result-observation-category</t>
@@ -1049,7 +1049,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.7/expansion</t>
+    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/cibmtr-priority-variables-2022</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1088,7 +1088,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|Device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|http://hl7.org/fhir/us/core/StructureDefinition/us-core-device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location)
 </t>
   </si>
   <si>
@@ -1119,7 +1119,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1286,7 +1286,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-us-core-3:SHALL use UCUM for coded quantity units. {ofType(Quantity).system.empty() or ofType(Quantity).system = 'http://unitsofmeasure.org'}us-core-4:SHOULD use Snomed CT for coded Results {ofType(CodeableConcept).coding.system.empty() or (ofType(CodeableConcept).coding.system contains 'http://snomed.info/sct')}</t>
+us-core-3:The system SHALL be UCUM for coded quantity units. {ofType(Quantity).system.empty() or ofType(Quantity).system = 'http://unitsofmeasure.org'}us-core-4:SHOULD use SNOMED CT for coded Results {ofType(CodeableConcept).coding.system.empty() or (ofType(CodeableConcept).coding.system contains 'http://snomed.info/sct')}</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -1320,7 +1320,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1408,7 +1408,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1441,7 +1441,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1481,7 +1481,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1530,7 +1530,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}us-core-22:SHALL use UCUM for coded quantity units. {(low.system.empty() or low.system = 'http://unitsofmeasure.org') and (high.system.empty() or high.system = 'http://unitsofmeasure.org')}</t>
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}us-core-22:The system SHALL be UCUM for coded quantity units. {(low.system.empty() or low.system = 'http://unitsofmeasure.org') and (high.system.empty() or high.system = 'http://unitsofmeasure.org')}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1565,7 +1565,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1615,7 +1615,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1648,7 +1648,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1685,7 +1685,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1707,7 +1707,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1768,7 +1768,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1821,6 +1821,9 @@
   </si>
   <si>
     <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2184,8 +2187,8 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="158.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.9921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -10716,7 +10719,7 @@
         <v>575</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>427</v>
+        <v>576</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10769,10 +10772,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10798,13 +10801,13 @@
         <v>82</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>482</v>
@@ -10856,7 +10859,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
